--- a/Excel-XLSX/UN-STP.xlsx
+++ b/Excel-XLSX/UN-STP.xlsx
@@ -30,7 +30,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>H367Pr</t>
+    <t>kUHy6v</t>
   </si>
   <si>
     <t>0</t>
